--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_individual_h_3.xlsx
@@ -658,7 +658,7 @@
         <v>0.008429030597149695</v>
       </c>
       <c r="C2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>14443972</v>
+        <v>4624709</v>
       </c>
       <c r="L2" t="n">
-        <v>8915298</v>
+        <v>2697549</v>
       </c>
       <c r="M2" t="n">
-        <v>2389107</v>
+        <v>692891</v>
       </c>
       <c r="N2" t="n">
-        <v>145414</v>
+        <v>33806</v>
       </c>
       <c r="O2" t="n">
-        <v>1386819</v>
+        <v>419672</v>
       </c>
       <c r="P2" t="n">
-        <v>532314</v>
+        <v>162300</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999781847000122</v>
+        <v>0.9999383687973022</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9547083973884583</v>
+        <v>0.9112957119941711</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9020754098892212</v>
+        <v>0.8239706754684448</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8741337060928345</v>
+        <v>0.7699995040893555</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7413256764411926</v>
+        <v>0.5165953636169434</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9003739356994629</v>
+        <v>0.8106439709663391</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9377982616424561</v>
+        <v>0.8795841932296753</v>
       </c>
       <c r="X2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="AG2" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AH2" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AI2" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566799402236938</v>
+        <v>0.9565494656562805</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112439155578613</v>
+        <v>0.9113017320632935</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581776022911072</v>
+        <v>0.8579359650611877</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626315712928772</v>
+        <v>0.6623888611793518</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020464420318604</v>
+        <v>0.9020065665245056</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
@@ -795,127 +795,127 @@
         <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>14443972</v>
+        <v>4624709</v>
       </c>
       <c r="E3" t="n">
-        <v>649040</v>
+        <v>398300</v>
       </c>
       <c r="F3" t="n">
-        <v>6937</v>
+        <v>4458</v>
       </c>
       <c r="G3" t="n">
-        <v>1143</v>
+        <v>660</v>
       </c>
       <c r="H3" t="n">
-        <v>267</v>
+        <v>205</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>30049453</v>
+        <v>10016233</v>
       </c>
       <c r="K3" t="n">
-        <v>33201836</v>
+        <v>10850735</v>
       </c>
       <c r="L3" t="n">
-        <v>38242140</v>
+        <v>12489116</v>
       </c>
       <c r="M3" t="n">
-        <v>45849507</v>
+        <v>15190512</v>
       </c>
       <c r="N3" t="n">
-        <v>48670862</v>
+        <v>16208837</v>
       </c>
       <c r="O3" t="n">
-        <v>47308413</v>
+        <v>15722392</v>
       </c>
       <c r="P3" t="n">
-        <v>48373647</v>
+        <v>16114080</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9564443230628967</v>
+        <v>0.9196625947952271</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9116907715797424</v>
+        <v>0.8264063596725464</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8546914458274841</v>
+        <v>0.743349552154541</v>
       </c>
       <c r="U3" t="n">
-        <v>0.544218122959137</v>
+        <v>0.3792929351329803</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9082365036010742</v>
+        <v>0.8242146968841553</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9180265069007874</v>
+        <v>0.8396231532096863</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="Z3" t="n">
-        <v>593526</v>
+        <v>197896</v>
       </c>
       <c r="AA3" t="n">
-        <v>25572</v>
+        <v>8540</v>
       </c>
       <c r="AB3" t="n">
-        <v>20336</v>
+        <v>6789</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30049866</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>33232195</v>
+        <v>11082162</v>
       </c>
       <c r="AG3" t="n">
-        <v>38343158</v>
+        <v>12776309</v>
       </c>
       <c r="AH3" t="n">
-        <v>45797268</v>
+        <v>15265103</v>
       </c>
       <c r="AI3" t="n">
-        <v>48631528</v>
+        <v>16210402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47312358</v>
+        <v>15770546</v>
       </c>
       <c r="AK3" t="n">
-        <v>48369192</v>
+        <v>16123045</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576433300971985</v>
+        <v>0.957583487033844</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.910033106803894</v>
+        <v>0.9099507331848145</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8577702045440674</v>
+        <v>0.8576524257659912</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.662115752696991</v>
+        <v>0.6619057655334473</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016677737236023</v>
+        <v>0.9016434550285339</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>646355</v>
+        <v>425785</v>
       </c>
       <c r="E4" t="n">
-        <v>8915298</v>
+        <v>2697549</v>
       </c>
       <c r="F4" t="n">
-        <v>205763</v>
+        <v>131698</v>
       </c>
       <c r="G4" t="n">
-        <v>4029</v>
+        <v>2955</v>
       </c>
       <c r="H4" t="n">
-        <v>7051</v>
+        <v>5884</v>
       </c>
       <c r="I4" t="n">
-        <v>366</v>
+        <v>321</v>
       </c>
       <c r="J4" t="n">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="K4" t="n">
-        <v>685226</v>
+        <v>450163</v>
       </c>
       <c r="L4" t="n">
-        <v>967798</v>
+        <v>576292</v>
       </c>
       <c r="M4" t="n">
-        <v>344007</v>
+        <v>206968</v>
       </c>
       <c r="N4" t="n">
-        <v>50740</v>
+        <v>31634</v>
       </c>
       <c r="O4" t="n">
-        <v>153451</v>
+        <v>98030</v>
       </c>
       <c r="P4" t="n">
-        <v>35307</v>
+        <v>22219</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999890923500061</v>
+        <v>0.9999691843986511</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9555755853652954</v>
+        <v>0.9154599905014038</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9068575501441956</v>
+        <v>0.8251867294311523</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8643032908439636</v>
+        <v>0.7564399242401123</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6276609897613525</v>
+        <v>0.4374227523803711</v>
       </c>
       <c r="V4" t="n">
-        <v>0.904288113117218</v>
+        <v>0.8173730969429016</v>
       </c>
       <c r="W4" t="n">
-        <v>0.927807092666626</v>
+        <v>0.8591392636299133</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>611398</v>
+        <v>204218</v>
       </c>
       <c r="Z4" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AA4" t="n">
-        <v>248302</v>
+        <v>83015</v>
       </c>
       <c r="AB4" t="n">
-        <v>16438</v>
+        <v>5489</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>654867</v>
+        <v>218736</v>
       </c>
       <c r="AG4" t="n">
-        <v>866780</v>
+        <v>289099</v>
       </c>
       <c r="AH4" t="n">
-        <v>396246</v>
+        <v>132377</v>
       </c>
       <c r="AI4" t="n">
-        <v>90074</v>
+        <v>30069</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149506</v>
+        <v>49876</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571613669395447</v>
+        <v>0.9570662379264832</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106380939483643</v>
+        <v>0.910625696182251</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579738140106201</v>
+        <v>0.8577942252159119</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6623735427856445</v>
+        <v>0.6621472835540771</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018570184707642</v>
+        <v>0.9018250107765198</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>23012</v>
+        <v>14789</v>
       </c>
       <c r="E5" t="n">
-        <v>274827</v>
+        <v>155003</v>
       </c>
       <c r="F5" t="n">
-        <v>2389107</v>
+        <v>692891</v>
       </c>
       <c r="G5" t="n">
-        <v>24844</v>
+        <v>15700</v>
       </c>
       <c r="H5" t="n">
-        <v>80746</v>
+        <v>51558</v>
       </c>
       <c r="I5" t="n">
-        <v>2750</v>
+        <v>2179</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>657766</v>
+        <v>403993</v>
       </c>
       <c r="L5" t="n">
-        <v>863564</v>
+        <v>566643</v>
       </c>
       <c r="M5" t="n">
-        <v>406179</v>
+        <v>239229</v>
       </c>
       <c r="N5" t="n">
-        <v>121784</v>
+        <v>55323</v>
       </c>
       <c r="O5" t="n">
-        <v>140117</v>
+        <v>89506</v>
       </c>
       <c r="P5" t="n">
-        <v>47532</v>
+        <v>31001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999915957450867</v>
+        <v>0.9999761581420898</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9725857377052307</v>
+        <v>0.9476927518844604</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9626167416572571</v>
+        <v>0.9300084114074707</v>
       </c>
       <c r="T5" t="n">
-        <v>0.984686553478241</v>
+        <v>0.9726755619049072</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9964783191680908</v>
+        <v>0.9946748614311218</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9940074682235718</v>
+        <v>0.9885155558586121</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9983090162277222</v>
+        <v>0.9967408776283264</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>23984</v>
+        <v>8010</v>
       </c>
       <c r="Z5" t="n">
-        <v>254565</v>
+        <v>84966</v>
       </c>
       <c r="AA5" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AB5" t="n">
-        <v>29795</v>
+        <v>9941</v>
       </c>
       <c r="AC5" t="n">
-        <v>87330</v>
+        <v>29135</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>639659</v>
+        <v>213300</v>
       </c>
       <c r="AG5" t="n">
-        <v>879774</v>
+        <v>293938</v>
       </c>
       <c r="AH5" t="n">
-        <v>397573</v>
+        <v>132685</v>
       </c>
       <c r="AI5" t="n">
-        <v>90282</v>
+        <v>30134</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150147</v>
+        <v>50081</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735750555992126</v>
+        <v>0.9735427498817444</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643478989601135</v>
+        <v>0.9642956852912903</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837958812713623</v>
+        <v>0.9837679862976074</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963183999061584</v>
+        <v>0.9963132739067078</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938832521438599</v>
+        <v>0.9938787817955017</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983758926391602</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>15784</v>
+        <v>9544</v>
       </c>
       <c r="E6" t="n">
-        <v>37793</v>
+        <v>17756</v>
       </c>
       <c r="F6" t="n">
-        <v>46593</v>
+        <v>16049</v>
       </c>
       <c r="G6" t="n">
-        <v>145414</v>
+        <v>33806</v>
       </c>
       <c r="H6" t="n">
-        <v>20514</v>
+        <v>11321</v>
       </c>
       <c r="I6" t="n">
-        <v>1074</v>
+        <v>633</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19318</v>
+        <v>6452</v>
       </c>
       <c r="Z6" t="n">
-        <v>16016</v>
+        <v>5347</v>
       </c>
       <c r="AA6" t="n">
-        <v>32584</v>
+        <v>10875</v>
       </c>
       <c r="AB6" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AC6" t="n">
-        <v>20921</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>5794</v>
+        <v>4993</v>
       </c>
       <c r="F7" t="n">
-        <v>83213</v>
+        <v>53590</v>
       </c>
       <c r="G7" t="n">
-        <v>19960</v>
+        <v>11817</v>
       </c>
       <c r="H7" t="n">
-        <v>1386819</v>
+        <v>419672</v>
       </c>
       <c r="I7" t="n">
-        <v>31100</v>
+        <v>19078</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2430</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>88798</v>
+        <v>29617</v>
       </c>
       <c r="AB7" t="n">
-        <v>22710</v>
+        <v>7585</v>
       </c>
       <c r="AC7" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>344</v>
+        <v>240</v>
       </c>
       <c r="F8" t="n">
-        <v>1501</v>
+        <v>1173</v>
       </c>
       <c r="G8" t="n">
-        <v>764</v>
+        <v>502</v>
       </c>
       <c r="H8" t="n">
-        <v>44873</v>
+        <v>29062</v>
       </c>
       <c r="I8" t="n">
-        <v>532314</v>
+        <v>162300</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
